--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3314"/>
+  <dimension ref="A1:D3315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73324,6 +73324,28 @@
         </is>
       </c>
     </row>
+    <row r="3315">
+      <c r="A3315" t="inlineStr">
+        <is>
+          <t>CVE-2026-84869</t>
+        </is>
+      </c>
+      <c r="B3315" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3315" t="inlineStr">
+        <is>
+          <t>ConnectWise Patches ScreenConnect Vulnerability Exploited in Worm-Like Attacks</t>
+        </is>
+      </c>
+      <c r="D3315" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/connectwise-patches-screenconnect-vulnerability-exploited-in-worm-like-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3315"/>
+  <dimension ref="A1:D3319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73346,6 +73346,94 @@
         </is>
       </c>
     </row>
+    <row r="3316">
+      <c r="A3316" t="inlineStr">
+        <is>
+          <t>CVE-2026-4201</t>
+        </is>
+      </c>
+      <c r="B3316" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3316" t="inlineStr">
+        <is>
+          <t>Three JFrog Artifactory Flaws Exploited for Backdoor Deployment</t>
+        </is>
+      </c>
+      <c r="D3316" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/three-jfrog-artifactory-flaws-exploited-for-backdoor-deployment/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3317">
+      <c r="A3317" t="inlineStr">
+        <is>
+          <t>CVE-2026-82329</t>
+        </is>
+      </c>
+      <c r="B3317" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3317" t="inlineStr">
+        <is>
+          <t>Three JFrog Artifactory Flaws Exploited for Backdoor Deployment</t>
+        </is>
+      </c>
+      <c r="D3317" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/three-jfrog-artifactory-flaws-exploited-for-backdoor-deployment/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3318">
+      <c r="A3318" t="inlineStr">
+        <is>
+          <t>CVE-2026-42016</t>
+        </is>
+      </c>
+      <c r="B3318" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3318" t="inlineStr">
+        <is>
+          <t>Three JFrog Artifactory Flaws Exploited for Backdoor Deployment</t>
+        </is>
+      </c>
+      <c r="D3318" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/three-jfrog-artifactory-flaws-exploited-for-backdoor-deployment/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3319">
+      <c r="A3319" t="inlineStr">
+        <is>
+          <t>CVE-2026-42018</t>
+        </is>
+      </c>
+      <c r="B3319" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3319" t="inlineStr">
+        <is>
+          <t>Three JFrog Artifactory Flaws Exploited for Backdoor Deployment</t>
+        </is>
+      </c>
+      <c r="D3319" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/three-jfrog-artifactory-flaws-exploited-for-backdoor-deployment/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3319"/>
+  <dimension ref="A1:D3320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73434,6 +73434,28 @@
         </is>
       </c>
     </row>
+    <row r="3320">
+      <c r="A3320" t="inlineStr">
+        <is>
+          <t>CVE-2026-51990</t>
+        </is>
+      </c>
+      <c r="B3320" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C3320" t="inlineStr">
+        <is>
+          <t>Chinese Hackers Exploit Critical Tencent Software Flaw for One-Click Code Execution</t>
+        </is>
+      </c>
+      <c r="D3320" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chinese-hackers-exploit-critical-tencent-software-flaw-for-one-click-code-execution/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3320"/>
+  <dimension ref="A1:D3324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73456,6 +73456,94 @@
         </is>
       </c>
     </row>
+    <row r="3321">
+      <c r="A3321" t="inlineStr">
+        <is>
+          <t>CVE-2025-20393</t>
+        </is>
+      </c>
+      <c r="B3321" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3321" t="inlineStr">
+        <is>
+          <t>Root RCE Zero-Day in Cisco Secure Email Gateway Under Active Exploitation</t>
+        </is>
+      </c>
+      <c r="D3321" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/root-rce-zero-day-in-cisco-secure-email-gateway-under-active-exploitation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3322">
+      <c r="A3322" t="inlineStr">
+        <is>
+          <t>CVE-2026-20079</t>
+        </is>
+      </c>
+      <c r="B3322" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3322" t="inlineStr">
+        <is>
+          <t>Root RCE Zero-Day in Cisco Secure Email Gateway Under Active Exploitation</t>
+        </is>
+      </c>
+      <c r="D3322" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/root-rce-zero-day-in-cisco-secure-email-gateway-under-active-exploitation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3323">
+      <c r="A3323" t="inlineStr">
+        <is>
+          <t>CVE-2026-20316</t>
+        </is>
+      </c>
+      <c r="B3323" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3323" t="inlineStr">
+        <is>
+          <t>Root RCE Zero-Day in Cisco Secure Email Gateway Under Active Exploitation</t>
+        </is>
+      </c>
+      <c r="D3323" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/root-rce-zero-day-in-cisco-secure-email-gateway-under-active-exploitation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3324">
+      <c r="A3324" t="inlineStr">
+        <is>
+          <t>CVE-2026-76461</t>
+        </is>
+      </c>
+      <c r="B3324" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3324" t="inlineStr">
+        <is>
+          <t>Root RCE Zero-Day in Cisco Secure Email Gateway Under Active Exploitation</t>
+        </is>
+      </c>
+      <c r="D3324" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/root-rce-zero-day-in-cisco-secure-email-gateway-under-active-exploitation/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3324"/>
+  <dimension ref="A1:D3325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73544,6 +73544,28 @@
         </is>
       </c>
     </row>
+    <row r="3325">
+      <c r="A3325" t="inlineStr">
+        <is>
+          <t>CVE-2022-3437</t>
+        </is>
+      </c>
+      <c r="B3325" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3325" t="inlineStr">
+        <is>
+          <t>Apple Patches 200 Vulnerabilities With New iOS 27, macOS Golden Gate 27 Releases</t>
+        </is>
+      </c>
+      <c r="D3325" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/apple-patches-200-vulnerabilities-with-new-ios-27-macos-golden-gate-27-releases/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3325"/>
+  <dimension ref="A1:D3326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73566,6 +73566,28 @@
         </is>
       </c>
     </row>
+    <row r="3326">
+      <c r="A3326" t="inlineStr">
+        <is>
+          <t>CVE-2026-64752</t>
+        </is>
+      </c>
+      <c r="B3326" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C3326" t="inlineStr">
+        <is>
+          <t>Apple Patches 200 Vulnerabilities With New iOS 27, macOS Golden Gate 27 Releases</t>
+        </is>
+      </c>
+      <c r="D3326" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/apple-patches-200-vulnerabilities-with-new-ios-27-macos-golden-gate-27-releases/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3326"/>
+  <dimension ref="A1:D3327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73588,6 +73588,28 @@
         </is>
       </c>
     </row>
+    <row r="3327">
+      <c r="A3327" t="inlineStr">
+        <is>
+          <t>CVE-2026-5430</t>
+        </is>
+      </c>
+      <c r="B3327" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3327" t="inlineStr">
+        <is>
+          <t>Enterprises Warned of Attacks Exploiting WSO2 Vulnerability</t>
+        </is>
+      </c>
+      <c r="D3327" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/enterprises-warned-of-attacks-exploiting-wso2-vulnerability/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3327"/>
+  <dimension ref="A1:D3328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73610,6 +73610,28 @@
         </is>
       </c>
     </row>
+    <row r="3328">
+      <c r="A3328" t="inlineStr">
+        <is>
+          <t>CVE-2026-87886</t>
+        </is>
+      </c>
+      <c r="B3328" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3328" t="inlineStr">
+        <is>
+          <t>Acronis Patches Exploited Vulnerability in cPanel Backup Plugin</t>
+        </is>
+      </c>
+      <c r="D3328" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/acronis-patches-exploited-vulnerability-in-cpanel-backup-plugin/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3328"/>
+  <dimension ref="A1:D3331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73632,6 +73632,72 @@
         </is>
       </c>
     </row>
+    <row r="3329">
+      <c r="A3329" t="inlineStr">
+        <is>
+          <t>CVE-2026-91726</t>
+        </is>
+      </c>
+      <c r="B3329" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3329" t="inlineStr">
+        <is>
+          <t>Chrome, Firefox Updates Patch 115 Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3329" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chrome-firefox-updates-patch-115-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3330">
+      <c r="A3330" t="inlineStr">
+        <is>
+          <t>CVE-2026-91749</t>
+        </is>
+      </c>
+      <c r="B3330" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3330" t="inlineStr">
+        <is>
+          <t>Chrome, Firefox Updates Patch 115 Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3330" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chrome-firefox-updates-patch-115-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3331">
+      <c r="A3331" t="inlineStr">
+        <is>
+          <t>CVE-2026-91721</t>
+        </is>
+      </c>
+      <c r="B3331" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3331" t="inlineStr">
+        <is>
+          <t>Chrome, Firefox Updates Patch 115 Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3331" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chrome-firefox-updates-patch-115-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3331"/>
+  <dimension ref="A1:D3333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73698,6 +73698,50 @@
         </is>
       </c>
     </row>
+    <row r="3332">
+      <c r="A3332" t="inlineStr">
+        <is>
+          <t>CVE-2026-78006</t>
+        </is>
+      </c>
+      <c r="B3332" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3332" t="inlineStr">
+        <is>
+          <t>Unauthenticated RCE Flaws Could Expose 200,000+ WordPress Sites to Takeover</t>
+        </is>
+      </c>
+      <c r="D3332" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/unauthenticated-rce-flaws-could-expose-200000-wordpress-sites-to-takeover/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3333">
+      <c r="A3333" t="inlineStr">
+        <is>
+          <t>CVE-2026-78159</t>
+        </is>
+      </c>
+      <c r="B3333" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3333" t="inlineStr">
+        <is>
+          <t>Unauthenticated RCE Flaws Could Expose 200,000+ WordPress Sites to Takeover</t>
+        </is>
+      </c>
+      <c r="D3333" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/unauthenticated-rce-flaws-could-expose-200000-wordpress-sites-to-takeover/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3333"/>
+  <dimension ref="A1:D3334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73742,6 +73742,28 @@
         </is>
       </c>
     </row>
+    <row r="3334">
+      <c r="A3334" t="inlineStr">
+        <is>
+          <t>CVE-2026-58704</t>
+        </is>
+      </c>
+      <c r="B3334" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C3334" t="inlineStr">
+        <is>
+          <t>Pixel Modem Zero-Day Exploited in Targeted Attacks</t>
+        </is>
+      </c>
+      <c r="D3334" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/pixel-modem-zero-day-exploited-in-targeted-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3334"/>
+  <dimension ref="A1:D3335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73764,6 +73764,28 @@
         </is>
       </c>
     </row>
+    <row r="3335">
+      <c r="A3335" t="inlineStr">
+        <is>
+          <t>CVE-2026-76460</t>
+        </is>
+      </c>
+      <c r="B3335" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3335" t="inlineStr">
+        <is>
+          <t>Active Exploitation Triggers Emergency Patch for Cisco ISE Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3335" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/active-exploitation-triggers-emergency-patch-for-cisco-ise-zero-day/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3335"/>
+  <dimension ref="A1:D3348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73786,6 +73786,292 @@
         </is>
       </c>
     </row>
+    <row r="3336">
+      <c r="A3336" t="inlineStr">
+        <is>
+          <t>CVE-2026-76163</t>
+        </is>
+      </c>
+      <c r="B3336" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3336" t="inlineStr">
+        <is>
+          <t>ISC Patches 14 Vulnerabilities in BIND 9 Security Update</t>
+        </is>
+      </c>
+      <c r="D3336" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/isc-patches-14-vulnerabilities-in-bind-9-security-update/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3337">
+      <c r="A3337" t="inlineStr">
+        <is>
+          <t>CVE-2026-77692</t>
+        </is>
+      </c>
+      <c r="B3337" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3337" t="inlineStr">
+        <is>
+          <t>ISC Patches 14 Vulnerabilities in BIND 9 Security Update</t>
+        </is>
+      </c>
+      <c r="D3337" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/isc-patches-14-vulnerabilities-in-bind-9-security-update/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3338">
+      <c r="A3338" t="inlineStr">
+        <is>
+          <t>CVE-2026-19667</t>
+        </is>
+      </c>
+      <c r="B3338" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3338" t="inlineStr">
+        <is>
+          <t>ISC Patches 14 Vulnerabilities in BIND 9 Security Update</t>
+        </is>
+      </c>
+      <c r="D3338" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/isc-patches-14-vulnerabilities-in-bind-9-security-update/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3339">
+      <c r="A3339" t="inlineStr">
+        <is>
+          <t>CVE-2026-81563</t>
+        </is>
+      </c>
+      <c r="B3339" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3339" t="inlineStr">
+        <is>
+          <t>ISC Patches 14 Vulnerabilities in BIND 9 Security Update</t>
+        </is>
+      </c>
+      <c r="D3339" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/isc-patches-14-vulnerabilities-in-bind-9-security-update/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3340">
+      <c r="A3340" t="inlineStr">
+        <is>
+          <t>CVE-2026-81736</t>
+        </is>
+      </c>
+      <c r="B3340" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3340" t="inlineStr">
+        <is>
+          <t>ISC Patches 14 Vulnerabilities in BIND 9 Security Update</t>
+        </is>
+      </c>
+      <c r="D3340" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/isc-patches-14-vulnerabilities-in-bind-9-security-update/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3341">
+      <c r="A3341" t="inlineStr">
+        <is>
+          <t>CVE-2026-19666</t>
+        </is>
+      </c>
+      <c r="B3341" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3341" t="inlineStr">
+        <is>
+          <t>ISC Patches 14 Vulnerabilities in BIND 9 Security Update</t>
+        </is>
+      </c>
+      <c r="D3341" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/isc-patches-14-vulnerabilities-in-bind-9-security-update/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3342">
+      <c r="A3342" t="inlineStr">
+        <is>
+          <t>CVE-2026-80274</t>
+        </is>
+      </c>
+      <c r="B3342" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3342" t="inlineStr">
+        <is>
+          <t>ISC Patches 14 Vulnerabilities in BIND 9 Security Update</t>
+        </is>
+      </c>
+      <c r="D3342" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/isc-patches-14-vulnerabilities-in-bind-9-security-update/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3343">
+      <c r="A3343" t="inlineStr">
+        <is>
+          <t>CVE-2026-20079</t>
+        </is>
+      </c>
+      <c r="B3343" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3343" t="inlineStr">
+        <is>
+          <t>Cisco Fixes Dozens of Flaws Across FMC, ISE and Nexus Dashboard</t>
+        </is>
+      </c>
+      <c r="D3343" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-fixes-dozens-of-flaws-across-fmc-ise-and-nexus-dashboard/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3344">
+      <c r="A3344" t="inlineStr">
+        <is>
+          <t>CVE-2026-20283</t>
+        </is>
+      </c>
+      <c r="B3344" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3344" t="inlineStr">
+        <is>
+          <t>Cisco Fixes Dozens of Flaws Across FMC, ISE and Nexus Dashboard</t>
+        </is>
+      </c>
+      <c r="D3344" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-fixes-dozens-of-flaws-across-fmc-ise-and-nexus-dashboard/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3345">
+      <c r="A3345" t="inlineStr">
+        <is>
+          <t>CVE-2026-20332</t>
+        </is>
+      </c>
+      <c r="B3345" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3345" t="inlineStr">
+        <is>
+          <t>Cisco Fixes Dozens of Flaws Across FMC, ISE and Nexus Dashboard</t>
+        </is>
+      </c>
+      <c r="D3345" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-fixes-dozens-of-flaws-across-fmc-ise-and-nexus-dashboard/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3346">
+      <c r="A3346" t="inlineStr">
+        <is>
+          <t>CVE-2026-20316</t>
+        </is>
+      </c>
+      <c r="B3346" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3346" t="inlineStr">
+        <is>
+          <t>Cisco Fixes Dozens of Flaws Across FMC, ISE and Nexus Dashboard</t>
+        </is>
+      </c>
+      <c r="D3346" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-fixes-dozens-of-flaws-across-fmc-ise-and-nexus-dashboard/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3347">
+      <c r="A3347" t="inlineStr">
+        <is>
+          <t>CVE-2026-20284</t>
+        </is>
+      </c>
+      <c r="B3347" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3347" t="inlineStr">
+        <is>
+          <t>Cisco Fixes Dozens of Flaws Across FMC, ISE and Nexus Dashboard</t>
+        </is>
+      </c>
+      <c r="D3347" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-fixes-dozens-of-flaws-across-fmc-ise-and-nexus-dashboard/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3348">
+      <c r="A3348" t="inlineStr">
+        <is>
+          <t>CVE-2026-20282</t>
+        </is>
+      </c>
+      <c r="B3348" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C3348" t="inlineStr">
+        <is>
+          <t>Cisco Fixes Dozens of Flaws Across FMC, ISE and Nexus Dashboard</t>
+        </is>
+      </c>
+      <c r="D3348" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-fixes-dozens-of-flaws-across-fmc-ise-and-nexus-dashboard/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3348"/>
+  <dimension ref="A1:D3349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74072,6 +74072,28 @@
         </is>
       </c>
     </row>
+    <row r="3349">
+      <c r="A3349" t="inlineStr">
+        <is>
+          <t>CVE-2026-91843</t>
+        </is>
+      </c>
+      <c r="B3349" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C3349" t="inlineStr">
+        <is>
+          <t>Check Point, Kaspersky, Tanium Patch Product Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3349" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/check-point-kaspersky-tanium-patch-product-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3349"/>
+  <dimension ref="A1:D3350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74094,6 +74094,28 @@
         </is>
       </c>
     </row>
+    <row r="3350">
+      <c r="A3350" t="inlineStr">
+        <is>
+          <t>CVE-2026-58138</t>
+        </is>
+      </c>
+      <c r="B3350" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C3350" t="inlineStr">
+        <is>
+          <t>Critical Orkes Conductor Vulnerability Exploited in Attacks</t>
+        </is>
+      </c>
+      <c r="D3350" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/critical-orkes-conductor-vulnerability-exploited-in-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3350"/>
+  <dimension ref="A1:D3351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74116,6 +74116,28 @@
         </is>
       </c>
     </row>
+    <row r="3351">
+      <c r="A3351" t="inlineStr">
+        <is>
+          <t>CVE-2026-85921</t>
+        </is>
+      </c>
+      <c r="B3351" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C3351" t="inlineStr">
+        <is>
+          <t>Microsoft Patches 18 Vulnerabilities in AI, Cloud Products</t>
+        </is>
+      </c>
+      <c r="D3351" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/microsoft-patches-18-vulnerabilities-in-ai-cloud-products/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3351"/>
+  <dimension ref="A1:D3354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74138,6 +74138,72 @@
         </is>
       </c>
     </row>
+    <row r="3352">
+      <c r="A3352" t="inlineStr">
+        <is>
+          <t>CVE-2026-15315</t>
+        </is>
+      </c>
+      <c r="B3352" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C3352" t="inlineStr">
+        <is>
+          <t>In Other News: Ransomware Developer Sentenced, Plugin4Shell AI Attack, Critical SAP Flaw</t>
+        </is>
+      </c>
+      <c r="D3352" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/in-other-news-ransomware-developer-sentenced-plugin4shell-ai-attack-critical-sap-flaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3353">
+      <c r="A3353" t="inlineStr">
+        <is>
+          <t>CVE-2026-44756</t>
+        </is>
+      </c>
+      <c r="B3353" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C3353" t="inlineStr">
+        <is>
+          <t>In Other News: Ransomware Developer Sentenced, Plugin4Shell AI Attack, Critical SAP Flaw</t>
+        </is>
+      </c>
+      <c r="D3353" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/in-other-news-ransomware-developer-sentenced-plugin4shell-ai-attack-critical-sap-flaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3354">
+      <c r="A3354" t="inlineStr">
+        <is>
+          <t>CVE-2026-15316</t>
+        </is>
+      </c>
+      <c r="B3354" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C3354" t="inlineStr">
+        <is>
+          <t>In Other News: Ransomware Developer Sentenced, Plugin4Shell AI Attack, Critical SAP Flaw</t>
+        </is>
+      </c>
+      <c r="D3354" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/in-other-news-ransomware-developer-sentenced-plugin4shell-ai-attack-critical-sap-flaw/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3354"/>
+  <dimension ref="A1:D3357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74204,6 +74204,72 @@
         </is>
       </c>
     </row>
+    <row r="3355">
+      <c r="A3355" t="inlineStr">
+        <is>
+          <t>CVE-2025-39682</t>
+        </is>
+      </c>
+      <c r="B3355" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C3355" t="inlineStr">
+        <is>
+          <t>Organizations Warned of 3 Exploited Linux Kernel Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3355" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/organizations-warned-of-3-exploited-linux-kernel-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3356">
+      <c r="A3356" t="inlineStr">
+        <is>
+          <t>CVE-2026-53266</t>
+        </is>
+      </c>
+      <c r="B3356" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C3356" t="inlineStr">
+        <is>
+          <t>Organizations Warned of 3 Exploited Linux Kernel Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3356" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/organizations-warned-of-3-exploited-linux-kernel-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3357">
+      <c r="A3357" t="inlineStr">
+        <is>
+          <t>CVE-2025-39964</t>
+        </is>
+      </c>
+      <c r="B3357" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C3357" t="inlineStr">
+        <is>
+          <t>Organizations Warned of 3 Exploited Linux Kernel Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3357" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/organizations-warned-of-3-exploited-linux-kernel-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3357"/>
+  <dimension ref="A1:D3358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74270,6 +74270,28 @@
         </is>
       </c>
     </row>
+    <row r="3358">
+      <c r="A3358" t="inlineStr">
+        <is>
+          <t>CVE-2026-7273</t>
+        </is>
+      </c>
+      <c r="B3358" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C3358" t="inlineStr">
+        <is>
+          <t>Recent ZyXEL Switch Vulnerability Exploited by Chinese Hackers</t>
+        </is>
+      </c>
+      <c r="D3358" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/recent-zyxel-switch-vulnerability-exploited-by-chinese-hackers/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3358"/>
+  <dimension ref="A1:D3360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74292,6 +74292,50 @@
         </is>
       </c>
     </row>
+    <row r="3359">
+      <c r="A3359" t="inlineStr">
+        <is>
+          <t>CVE-2026-85102</t>
+        </is>
+      </c>
+      <c r="B3359" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3359" t="inlineStr">
+        <is>
+          <t>Check Point Patches Exploited Management Server Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3359" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/check-point-patches-exploited-management-server-zero-day/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3360">
+      <c r="A3360" t="inlineStr">
+        <is>
+          <t>CVE-2026-93616</t>
+        </is>
+      </c>
+      <c r="B3360" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3360" t="inlineStr">
+        <is>
+          <t>Check Point Patches Exploited Management Server Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3360" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/check-point-patches-exploited-management-server-zero-day/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3360"/>
+  <dimension ref="A1:D3361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74336,6 +74336,28 @@
         </is>
       </c>
     </row>
+    <row r="3361">
+      <c r="A3361" t="inlineStr">
+        <is>
+          <t>CVE-2026-94127</t>
+        </is>
+      </c>
+      <c r="B3361" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3361" t="inlineStr">
+        <is>
+          <t>Critical F5 BIG-IP Vulnerability Exploited as Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3361" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/critical-f5-big-ip-vulnerability-exploited-as-zero-day/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3361"/>
+  <dimension ref="A1:D3362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74358,6 +74358,28 @@
         </is>
       </c>
     </row>
+    <row r="3362">
+      <c r="A3362" t="inlineStr">
+        <is>
+          <t>CVE-2026-93952</t>
+        </is>
+      </c>
+      <c r="B3362" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3362" t="inlineStr">
+        <is>
+          <t>Arista Urges Immediate Patching of Exploited VCO Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3362" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/arista-urges-immediate-patching-of-exploited-vco-zero-day/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3362"/>
+  <dimension ref="A1:D3371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74380,6 +74380,204 @@
         </is>
       </c>
     </row>
+    <row r="3363">
+      <c r="A3363" t="inlineStr">
+        <is>
+          <t>CVE-2026-75684</t>
+        </is>
+      </c>
+      <c r="B3363" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3363" t="inlineStr">
+        <is>
+          <t>Adobe Patches Critical Flaws in Connect, AEM Forms</t>
+        </is>
+      </c>
+      <c r="D3363" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/adobe-patches-critical-flaws-in-connect-aem-forms/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3364">
+      <c r="A3364" t="inlineStr">
+        <is>
+          <t>CVE-2026-81995</t>
+        </is>
+      </c>
+      <c r="B3364" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3364" t="inlineStr">
+        <is>
+          <t>Adobe Patches Critical Flaws in Connect, AEM Forms</t>
+        </is>
+      </c>
+      <c r="D3364" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/adobe-patches-critical-flaws-in-connect-aem-forms/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3365">
+      <c r="A3365" t="inlineStr">
+        <is>
+          <t>CVE-2026-75697</t>
+        </is>
+      </c>
+      <c r="B3365" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3365" t="inlineStr">
+        <is>
+          <t>Adobe Patches Critical Flaws in Connect, AEM Forms</t>
+        </is>
+      </c>
+      <c r="D3365" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/adobe-patches-critical-flaws-in-connect-aem-forms/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3366">
+      <c r="A3366" t="inlineStr">
+        <is>
+          <t>CVE-2026-75689</t>
+        </is>
+      </c>
+      <c r="B3366" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3366" t="inlineStr">
+        <is>
+          <t>Adobe Patches Critical Flaws in Connect, AEM Forms</t>
+        </is>
+      </c>
+      <c r="D3366" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/adobe-patches-critical-flaws-in-connect-aem-forms/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3367">
+      <c r="A3367" t="inlineStr">
+        <is>
+          <t>CVE-2026-82000</t>
+        </is>
+      </c>
+      <c r="B3367" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3367" t="inlineStr">
+        <is>
+          <t>Adobe Patches Critical Flaws in Connect, AEM Forms</t>
+        </is>
+      </c>
+      <c r="D3367" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/adobe-patches-critical-flaws-in-connect-aem-forms/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3368">
+      <c r="A3368" t="inlineStr">
+        <is>
+          <t>CVE-2026-75745</t>
+        </is>
+      </c>
+      <c r="B3368" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3368" t="inlineStr">
+        <is>
+          <t>Adobe Patches Critical Flaws in Connect, AEM Forms</t>
+        </is>
+      </c>
+      <c r="D3368" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/adobe-patches-critical-flaws-in-connect-aem-forms/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3369">
+      <c r="A3369" t="inlineStr">
+        <is>
+          <t>CVE-2026-75682</t>
+        </is>
+      </c>
+      <c r="B3369" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3369" t="inlineStr">
+        <is>
+          <t>Adobe Patches Critical Flaws in Connect, AEM Forms</t>
+        </is>
+      </c>
+      <c r="D3369" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/adobe-patches-critical-flaws-in-connect-aem-forms/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3370">
+      <c r="A3370" t="inlineStr">
+        <is>
+          <t>CVE-2026-75698</t>
+        </is>
+      </c>
+      <c r="B3370" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3370" t="inlineStr">
+        <is>
+          <t>Adobe Patches Critical Flaws in Connect, AEM Forms</t>
+        </is>
+      </c>
+      <c r="D3370" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/adobe-patches-critical-flaws-in-connect-aem-forms/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3371">
+      <c r="A3371" t="inlineStr">
+        <is>
+          <t>CVE-2026-75686</t>
+        </is>
+      </c>
+      <c r="B3371" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3371" t="inlineStr">
+        <is>
+          <t>Adobe Patches Critical Flaws in Connect, AEM Forms</t>
+        </is>
+      </c>
+      <c r="D3371" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/adobe-patches-critical-flaws-in-connect-aem-forms/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3371"/>
+  <dimension ref="A1:D3372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74578,6 +74578,28 @@
         </is>
       </c>
     </row>
+    <row r="3372">
+      <c r="A3372" t="inlineStr">
+        <is>
+          <t>CVE-2026-87902</t>
+        </is>
+      </c>
+      <c r="B3372" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3372" t="inlineStr">
+        <is>
+          <t>Critical WordPress Vulnerability Exploited Immediately After Disclosure</t>
+        </is>
+      </c>
+      <c r="D3372" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/critical-wordpress-vulnerability-exploited-immediately-after-disclosure/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3372"/>
+  <dimension ref="A1:D3375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74600,6 +74600,72 @@
         </is>
       </c>
     </row>
+    <row r="3373">
+      <c r="A3373" t="inlineStr">
+        <is>
+          <t>CVE-2026-28325</t>
+        </is>
+      </c>
+      <c r="B3373" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3373" t="inlineStr">
+        <is>
+          <t>SolarWinds Patches Critical RCE Flaws in Observability Self-Hosted</t>
+        </is>
+      </c>
+      <c r="D3373" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/solarwinds-patches-critical-rce-flaws-in-observability-self-hosted/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3374">
+      <c r="A3374" t="inlineStr">
+        <is>
+          <t>CVE-2026-28324</t>
+        </is>
+      </c>
+      <c r="B3374" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3374" t="inlineStr">
+        <is>
+          <t>SolarWinds Patches Critical RCE Flaws in Observability Self-Hosted</t>
+        </is>
+      </c>
+      <c r="D3374" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/solarwinds-patches-critical-rce-flaws-in-observability-self-hosted/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3375">
+      <c r="A3375" t="inlineStr">
+        <is>
+          <t>CVE-2026-28326</t>
+        </is>
+      </c>
+      <c r="B3375" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3375" t="inlineStr">
+        <is>
+          <t>SolarWinds Patches Critical RCE Flaws in Observability Self-Hosted</t>
+        </is>
+      </c>
+      <c r="D3375" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/solarwinds-patches-critical-rce-flaws-in-observability-self-hosted/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3375"/>
+  <dimension ref="A1:D3379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74666,6 +74666,94 @@
         </is>
       </c>
     </row>
+    <row r="3376">
+      <c r="A3376" t="inlineStr">
+        <is>
+          <t>CVE-2025-68461</t>
+        </is>
+      </c>
+      <c r="B3376" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3376" t="inlineStr">
+        <is>
+          <t>Roundcube Webmail Vulnerability in Attackers’ Crosshairs</t>
+        </is>
+      </c>
+      <c r="D3376" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/roundcube-webmail-vulnerability-in-attackers-crosshairs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3377">
+      <c r="A3377" t="inlineStr">
+        <is>
+          <t>CVE-2026-48842</t>
+        </is>
+      </c>
+      <c r="B3377" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3377" t="inlineStr">
+        <is>
+          <t>Roundcube Webmail Vulnerability in Attackers’ Crosshairs</t>
+        </is>
+      </c>
+      <c r="D3377" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/roundcube-webmail-vulnerability-in-attackers-crosshairs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3378">
+      <c r="A3378" t="inlineStr">
+        <is>
+          <t>CVE-2025-49113</t>
+        </is>
+      </c>
+      <c r="B3378" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3378" t="inlineStr">
+        <is>
+          <t>Roundcube Webmail Vulnerability in Attackers’ Crosshairs</t>
+        </is>
+      </c>
+      <c r="D3378" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/roundcube-webmail-vulnerability-in-attackers-crosshairs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3379">
+      <c r="A3379" t="inlineStr">
+        <is>
+          <t>CVE-2024-37383</t>
+        </is>
+      </c>
+      <c r="B3379" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3379" t="inlineStr">
+        <is>
+          <t>Roundcube Webmail Vulnerability in Attackers’ Crosshairs</t>
+        </is>
+      </c>
+      <c r="D3379" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/roundcube-webmail-vulnerability-in-attackers-crosshairs/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3379"/>
+  <dimension ref="A1:D3389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74581,176 +74581,396 @@
     <row r="3372">
       <c r="A3372" t="inlineStr">
         <is>
-          <t>CVE-2026-87902</t>
+          <t>CVE-2026-65660</t>
         </is>
       </c>
       <c r="B3372" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C3372" t="inlineStr">
         <is>
-          <t>Critical WordPress Vulnerability Exploited Immediately After Disclosure</t>
+          <t>Adobe Patches Critical Flaws in Connect, AEM Forms</t>
         </is>
       </c>
       <c r="D3372" t="inlineStr">
         <is>
-          <t>https://www.securityweek.com/critical-wordpress-vulnerability-exploited-immediately-after-disclosure/</t>
+          <t>https://www.securityweek.com/adobe-patches-critical-flaws-in-connect-aem-forms/</t>
         </is>
       </c>
     </row>
     <row r="3373">
       <c r="A3373" t="inlineStr">
         <is>
-          <t>CVE-2026-28325</t>
+          <t>CVE-2026-65660</t>
         </is>
       </c>
       <c r="B3373" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C3373" t="inlineStr">
         <is>
-          <t>SolarWinds Patches Critical RCE Flaws in Observability Self-Hosted</t>
+          <t>Chrome 154 Patches 108 Vulnerabilities</t>
         </is>
       </c>
       <c r="D3373" t="inlineStr">
         <is>
-          <t>https://www.securityweek.com/solarwinds-patches-critical-rce-flaws-in-observability-self-hosted/</t>
+          <t>https://www.securityweek.com/chrome-154-patches-108-vulnerabilities/</t>
         </is>
       </c>
     </row>
     <row r="3374">
       <c r="A3374" t="inlineStr">
         <is>
-          <t>CVE-2026-28324</t>
+          <t>CVE-2026-65660</t>
         </is>
       </c>
       <c r="B3374" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C3374" t="inlineStr">
         <is>
-          <t>SolarWinds Patches Critical RCE Flaws in Observability Self-Hosted</t>
+          <t>Arista Urges Immediate Patching of Exploited VCO Zero-Day</t>
         </is>
       </c>
       <c r="D3374" t="inlineStr">
         <is>
-          <t>https://www.securityweek.com/solarwinds-patches-critical-rce-flaws-in-observability-self-hosted/</t>
+          <t>https://www.securityweek.com/arista-urges-immediate-patching-of-exploited-vco-zero-day/</t>
         </is>
       </c>
     </row>
     <row r="3375">
       <c r="A3375" t="inlineStr">
         <is>
-          <t>CVE-2026-28326</t>
+          <t>CVE-2026-65660</t>
         </is>
       </c>
       <c r="B3375" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C3375" t="inlineStr">
         <is>
-          <t>SolarWinds Patches Critical RCE Flaws in Observability Self-Hosted</t>
+          <t>Critical F5 BIG-IP Vulnerability Exploited as Zero-Day</t>
         </is>
       </c>
       <c r="D3375" t="inlineStr">
         <is>
-          <t>https://www.securityweek.com/solarwinds-patches-critical-rce-flaws-in-observability-self-hosted/</t>
+          <t>https://www.securityweek.com/critical-f5-big-ip-vulnerability-exploited-as-zero-day/</t>
         </is>
       </c>
     </row>
     <row r="3376">
       <c r="A3376" t="inlineStr">
         <is>
-          <t>CVE-2025-68461</t>
+          <t>CVE-2026-65660</t>
         </is>
       </c>
       <c r="B3376" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C3376" t="inlineStr">
         <is>
-          <t>Roundcube Webmail Vulnerability in Attackers’ Crosshairs</t>
+          <t>Check Point Patches Exploited Management Server Zero-Day</t>
         </is>
       </c>
       <c r="D3376" t="inlineStr">
         <is>
-          <t>https://www.securityweek.com/roundcube-webmail-vulnerability-in-attackers-crosshairs/</t>
+          <t>https://www.securityweek.com/check-point-patches-exploited-management-server-zero-day/</t>
         </is>
       </c>
     </row>
     <row r="3377">
       <c r="A3377" t="inlineStr">
         <is>
-          <t>CVE-2026-48842</t>
+          <t>CVE-2026-87902</t>
         </is>
       </c>
       <c r="B3377" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C3377" t="inlineStr">
         <is>
-          <t>Roundcube Webmail Vulnerability in Attackers’ Crosshairs</t>
+          <t>Critical WordPress Vulnerability Exploited Immediately After Disclosure</t>
         </is>
       </c>
       <c r="D3377" t="inlineStr">
         <is>
-          <t>https://www.securityweek.com/roundcube-webmail-vulnerability-in-attackers-crosshairs/</t>
+          <t>https://www.securityweek.com/critical-wordpress-vulnerability-exploited-immediately-after-disclosure/</t>
         </is>
       </c>
     </row>
     <row r="3378">
       <c r="A3378" t="inlineStr">
         <is>
-          <t>CVE-2025-49113</t>
+          <t>CVE-2026-28325</t>
         </is>
       </c>
       <c r="B3378" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C3378" t="inlineStr">
         <is>
-          <t>Roundcube Webmail Vulnerability in Attackers’ Crosshairs</t>
+          <t>SolarWinds Patches Critical RCE Flaws in Observability Self-Hosted</t>
         </is>
       </c>
       <c r="D3378" t="inlineStr">
         <is>
-          <t>https://www.securityweek.com/roundcube-webmail-vulnerability-in-attackers-crosshairs/</t>
+          <t>https://www.securityweek.com/solarwinds-patches-critical-rce-flaws-in-observability-self-hosted/</t>
         </is>
       </c>
     </row>
     <row r="3379">
       <c r="A3379" t="inlineStr">
         <is>
+          <t>CVE-2026-28324</t>
+        </is>
+      </c>
+      <c r="B3379" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3379" t="inlineStr">
+        <is>
+          <t>SolarWinds Patches Critical RCE Flaws in Observability Self-Hosted</t>
+        </is>
+      </c>
+      <c r="D3379" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/solarwinds-patches-critical-rce-flaws-in-observability-self-hosted/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3380">
+      <c r="A3380" t="inlineStr">
+        <is>
+          <t>CVE-2026-28326</t>
+        </is>
+      </c>
+      <c r="B3380" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3380" t="inlineStr">
+        <is>
+          <t>SolarWinds Patches Critical RCE Flaws in Observability Self-Hosted</t>
+        </is>
+      </c>
+      <c r="D3380" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/solarwinds-patches-critical-rce-flaws-in-observability-self-hosted/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3381">
+      <c r="A3381" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3381" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3381" t="inlineStr">
+        <is>
+          <t>SolarWinds Patches Critical RCE Flaws in Observability Self-Hosted</t>
+        </is>
+      </c>
+      <c r="D3381" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/solarwinds-patches-critical-rce-flaws-in-observability-self-hosted/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3382">
+      <c r="A3382" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3382" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C3382" t="inlineStr">
+        <is>
+          <t>Critical WordPress Vulnerability Exploited Immediately After Disclosure</t>
+        </is>
+      </c>
+      <c r="D3382" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/critical-wordpress-vulnerability-exploited-immediately-after-disclosure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3383">
+      <c r="A3383" t="inlineStr">
+        <is>
+          <t>CVE-2025-68461</t>
+        </is>
+      </c>
+      <c r="B3383" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3383" t="inlineStr">
+        <is>
+          <t>Roundcube Webmail Vulnerability in Attackers’ Crosshairs</t>
+        </is>
+      </c>
+      <c r="D3383" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/roundcube-webmail-vulnerability-in-attackers-crosshairs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3384">
+      <c r="A3384" t="inlineStr">
+        <is>
+          <t>CVE-2026-48842</t>
+        </is>
+      </c>
+      <c r="B3384" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3384" t="inlineStr">
+        <is>
+          <t>Roundcube Webmail Vulnerability in Attackers’ Crosshairs</t>
+        </is>
+      </c>
+      <c r="D3384" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/roundcube-webmail-vulnerability-in-attackers-crosshairs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3385">
+      <c r="A3385" t="inlineStr">
+        <is>
+          <t>CVE-2025-49113</t>
+        </is>
+      </c>
+      <c r="B3385" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3385" t="inlineStr">
+        <is>
+          <t>Roundcube Webmail Vulnerability in Attackers’ Crosshairs</t>
+        </is>
+      </c>
+      <c r="D3385" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/roundcube-webmail-vulnerability-in-attackers-crosshairs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3386">
+      <c r="A3386" t="inlineStr">
+        <is>
           <t>CVE-2024-37383</t>
         </is>
       </c>
-      <c r="B3379" t="inlineStr">
+      <c r="B3386" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="C3379" t="inlineStr">
+      <c r="C3386" t="inlineStr">
         <is>
           <t>Roundcube Webmail Vulnerability in Attackers’ Crosshairs</t>
         </is>
       </c>
-      <c r="D3379" t="inlineStr">
+      <c r="D3386" t="inlineStr">
         <is>
           <t>https://www.securityweek.com/roundcube-webmail-vulnerability-in-attackers-crosshairs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3387">
+      <c r="A3387" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3387" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3387" t="inlineStr">
+        <is>
+          <t>‘SalesBleed’ Flaws in Salesforce Agentforce Enabled Zero-Click Data Exfiltration</t>
+        </is>
+      </c>
+      <c r="D3387" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/salesbleed-flaws-in-salesforce-agentforce-enabled-zero-click-data-exfiltration/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3388">
+      <c r="A3388" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3388" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C3388" t="inlineStr">
+        <is>
+          <t>Roundcube Webmail Vulnerability in Attackers’ Crosshairs</t>
+        </is>
+      </c>
+      <c r="D3388" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/roundcube-webmail-vulnerability-in-attackers-crosshairs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3389">
+      <c r="A3389" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3389" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C3389" t="inlineStr">
+        <is>
+          <t>Microsoft SharePoint Flaw CVE-2026-65660 Now Exploited in Attacks</t>
+        </is>
+      </c>
+      <c r="D3389" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/microsoft-sharepoint-flaw-cve-2026-65660-now-exploited-in-attacks/</t>
         </is>
       </c>
     </row>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3389"/>
+  <dimension ref="A1:D3395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74974,6 +74974,138 @@
         </is>
       </c>
     </row>
+    <row r="3390">
+      <c r="A3390" t="inlineStr">
+        <is>
+          <t>CVE-2026-88772</t>
+        </is>
+      </c>
+      <c r="B3390" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3390" t="inlineStr">
+        <is>
+          <t>Citrix Confirms 2 NetScaler Zero-Days After Admins Pulled the Plug</t>
+        </is>
+      </c>
+      <c r="D3390" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-confirms-2-netscaler-zero-days-after-admins-pulled-the-plug/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3391">
+      <c r="A3391" t="inlineStr">
+        <is>
+          <t>CVE-2026-8452</t>
+        </is>
+      </c>
+      <c r="B3391" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3391" t="inlineStr">
+        <is>
+          <t>Citrix Confirms 2 NetScaler Zero-Days After Admins Pulled the Plug</t>
+        </is>
+      </c>
+      <c r="D3391" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-confirms-2-netscaler-zero-days-after-admins-pulled-the-plug/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3392">
+      <c r="A3392" t="inlineStr">
+        <is>
+          <t>CVE-2026-88771</t>
+        </is>
+      </c>
+      <c r="B3392" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3392" t="inlineStr">
+        <is>
+          <t>Citrix Confirms 2 NetScaler Zero-Days After Admins Pulled the Plug</t>
+        </is>
+      </c>
+      <c r="D3392" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-confirms-2-netscaler-zero-days-after-admins-pulled-the-plug/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3393">
+      <c r="A3393" t="inlineStr">
+        <is>
+          <t>CVE-2026-88778</t>
+        </is>
+      </c>
+      <c r="B3393" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3393" t="inlineStr">
+        <is>
+          <t>Citrix Confirms 2 NetScaler Zero-Days After Admins Pulled the Plug</t>
+        </is>
+      </c>
+      <c r="D3393" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-confirms-2-netscaler-zero-days-after-admins-pulled-the-plug/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3394">
+      <c r="A3394" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3394" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3394" t="inlineStr">
+        <is>
+          <t>Citrix Confirms 2 NetScaler Zero-Days After Admins Pulled the Plug</t>
+        </is>
+      </c>
+      <c r="D3394" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-confirms-2-netscaler-zero-days-after-admins-pulled-the-plug/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3395">
+      <c r="A3395" t="inlineStr">
+        <is>
+          <t>CVE-2026-19490</t>
+        </is>
+      </c>
+      <c r="B3395" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3395" t="inlineStr">
+        <is>
+          <t>Citrix Confirms 2 NetScaler Zero-Days After Admins Pulled the Plug</t>
+        </is>
+      </c>
+      <c r="D3395" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-confirms-2-netscaler-zero-days-after-admins-pulled-the-plug/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3395"/>
+  <dimension ref="A1:D3396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75106,6 +75106,28 @@
         </is>
       </c>
     </row>
+    <row r="3396">
+      <c r="A3396" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3396" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3396" t="inlineStr">
+        <is>
+          <t>Kiteworks Urges Server Shutdown, Finds Advanced Forms Vulnerability</t>
+        </is>
+      </c>
+      <c r="D3396" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/kiteworks-urges-server-shutdown-finds-advanced-forms-vulnerability/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3396"/>
+  <dimension ref="A1:D3398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75128,6 +75128,50 @@
         </is>
       </c>
     </row>
+    <row r="3397">
+      <c r="A3397" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3397" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3397" t="inlineStr">
+        <is>
+          <t>Google Warns of ShinyHunters’ Fresh Oracle PeopleSoft Campaign</t>
+        </is>
+      </c>
+      <c r="D3397" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/google-warns-of-shinyhunters-fresh-oracle-peoplesoft-campaign/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3398">
+      <c r="A3398" t="inlineStr">
+        <is>
+          <t>CVE-2026-35273</t>
+        </is>
+      </c>
+      <c r="B3398" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C3398" t="inlineStr">
+        <is>
+          <t>Google Warns of ShinyHunters’ Fresh Oracle PeopleSoft Campaign</t>
+        </is>
+      </c>
+      <c r="D3398" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/google-warns-of-shinyhunters-fresh-oracle-peoplesoft-campaign/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3398"/>
+  <dimension ref="A1:D3402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75172,6 +75172,94 @@
         </is>
       </c>
     </row>
+    <row r="3399">
+      <c r="A3399" t="inlineStr">
+        <is>
+          <t>CVE-2025-43300</t>
+        </is>
+      </c>
+      <c r="B3399" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3399" t="inlineStr">
+        <is>
+          <t>Apple Patches Meta-Reported Zero-Day Linked to ‘Extremely Sophisticated Attack’</t>
+        </is>
+      </c>
+      <c r="D3399" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/apple-patches-meta-reported-zero-day-linked-to-extremely-sophisticated-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3400">
+      <c r="A3400" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3400" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3400" t="inlineStr">
+        <is>
+          <t>Apple Patches Meta-Reported Zero-Day Linked to ‘Extremely Sophisticated Attack’</t>
+        </is>
+      </c>
+      <c r="D3400" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/apple-patches-meta-reported-zero-day-linked-to-extremely-sophisticated-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3401">
+      <c r="A3401" t="inlineStr">
+        <is>
+          <t>CVE-2026-86950</t>
+        </is>
+      </c>
+      <c r="B3401" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3401" t="inlineStr">
+        <is>
+          <t>Apple Patches Meta-Reported Zero-Day Linked to ‘Extremely Sophisticated Attack’</t>
+        </is>
+      </c>
+      <c r="D3401" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/apple-patches-meta-reported-zero-day-linked-to-extremely-sophisticated-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3402">
+      <c r="A3402" t="inlineStr">
+        <is>
+          <t>CVE-2025-55177</t>
+        </is>
+      </c>
+      <c r="B3402" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3402" t="inlineStr">
+        <is>
+          <t>Apple Patches Meta-Reported Zero-Day Linked to ‘Extremely Sophisticated Attack’</t>
+        </is>
+      </c>
+      <c r="D3402" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/apple-patches-meta-reported-zero-day-linked-to-extremely-sophisticated-attack/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3402"/>
+  <dimension ref="A1:D3403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75260,6 +75260,28 @@
         </is>
       </c>
     </row>
+    <row r="3403">
+      <c r="A3403" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3403" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3403" t="inlineStr">
+        <is>
+          <t>New Spectre v2 Variant Exposes Intel, AMD, Arm CPUs to Data Leaks</t>
+        </is>
+      </c>
+      <c r="D3403" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/new-spectre-v2-variant-exposes-intel-amd-arm-cpus-to-data-leaks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3403"/>
+  <dimension ref="A1:D3409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75282,6 +75282,138 @@
         </is>
       </c>
     </row>
+    <row r="3404">
+      <c r="A3404" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3404" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3404" t="inlineStr">
+        <is>
+          <t>High-Severity Vulnerabilities Patched in OpenSSL, WolfSSL</t>
+        </is>
+      </c>
+      <c r="D3404" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/high-severity-vulnerabilities-patched-in-openssl-wolfssl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3405">
+      <c r="A3405" t="inlineStr">
+        <is>
+          <t>CVE-2026-93302</t>
+        </is>
+      </c>
+      <c r="B3405" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3405" t="inlineStr">
+        <is>
+          <t>High-Severity Vulnerabilities Patched in OpenSSL, WolfSSL</t>
+        </is>
+      </c>
+      <c r="D3405" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/high-severity-vulnerabilities-patched-in-openssl-wolfssl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3406">
+      <c r="A3406" t="inlineStr">
+        <is>
+          <t>CVE-2026-84783</t>
+        </is>
+      </c>
+      <c r="B3406" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3406" t="inlineStr">
+        <is>
+          <t>High-Severity Vulnerabilities Patched in OpenSSL, WolfSSL</t>
+        </is>
+      </c>
+      <c r="D3406" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/high-severity-vulnerabilities-patched-in-openssl-wolfssl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3407">
+      <c r="A3407" t="inlineStr">
+        <is>
+          <t>CVE-2026-84782</t>
+        </is>
+      </c>
+      <c r="B3407" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3407" t="inlineStr">
+        <is>
+          <t>High-Severity Vulnerabilities Patched in OpenSSL, WolfSSL</t>
+        </is>
+      </c>
+      <c r="D3407" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/high-severity-vulnerabilities-patched-in-openssl-wolfssl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3408">
+      <c r="A3408" t="inlineStr">
+        <is>
+          <t>CVE-2026-89102</t>
+        </is>
+      </c>
+      <c r="B3408" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3408" t="inlineStr">
+        <is>
+          <t>High-Severity Vulnerabilities Patched in OpenSSL, WolfSSL</t>
+        </is>
+      </c>
+      <c r="D3408" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/high-severity-vulnerabilities-patched-in-openssl-wolfssl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3409">
+      <c r="A3409" t="inlineStr">
+        <is>
+          <t>CVE-2026-89136</t>
+        </is>
+      </c>
+      <c r="B3409" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3409" t="inlineStr">
+        <is>
+          <t>High-Severity Vulnerabilities Patched in OpenSSL, WolfSSL</t>
+        </is>
+      </c>
+      <c r="D3409" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/high-severity-vulnerabilities-patched-in-openssl-wolfssl/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3409"/>
+  <dimension ref="A1:D3413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75414,6 +75414,94 @@
         </is>
       </c>
     </row>
+    <row r="3410">
+      <c r="A3410" t="inlineStr">
+        <is>
+          <t>CVE-2026-88771</t>
+        </is>
+      </c>
+      <c r="B3410" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3410" t="inlineStr">
+        <is>
+          <t>Government, Finance Orgs Targeted in Weeks-Long NetScaler Zero-Day Attacks</t>
+        </is>
+      </c>
+      <c r="D3410" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/government-finance-orgs-targeted-in-weeks-long-netscaler-zero-day-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3411">
+      <c r="A3411" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3411" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3411" t="inlineStr">
+        <is>
+          <t>Government, Finance Orgs Targeted in Weeks-Long NetScaler Zero-Day Attacks</t>
+        </is>
+      </c>
+      <c r="D3411" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/government-finance-orgs-targeted-in-weeks-long-netscaler-zero-day-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3412">
+      <c r="A3412" t="inlineStr">
+        <is>
+          <t>CVE-2026-88772</t>
+        </is>
+      </c>
+      <c r="B3412" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3412" t="inlineStr">
+        <is>
+          <t>Government, Finance Orgs Targeted in Weeks-Long NetScaler Zero-Day Attacks</t>
+        </is>
+      </c>
+      <c r="D3412" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/government-finance-orgs-targeted-in-weeks-long-netscaler-zero-day-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3413">
+      <c r="A3413" t="inlineStr">
+        <is>
+          <t>CVE-2026-102331</t>
+        </is>
+      </c>
+      <c r="B3413" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3413" t="inlineStr">
+        <is>
+          <t>Chrome, Firefox Updates Patch Over 100 Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3413" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chrome-firefox-updates-patch-over-100-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3413"/>
+  <dimension ref="A1:D3416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75502,6 +75502,72 @@
         </is>
       </c>
     </row>
+    <row r="3414">
+      <c r="A3414" t="inlineStr">
+        <is>
+          <t>CVE-2026-86102</t>
+        </is>
+      </c>
+      <c r="B3414" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3414" t="inlineStr">
+        <is>
+          <t>WatchGuard Patches Critical Fireware OS Code Injection Vulnerability</t>
+        </is>
+      </c>
+      <c r="D3414" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/watchguard-patches-critical-fireware-os-code-injection-vulnerability/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3415">
+      <c r="A3415" t="inlineStr">
+        <is>
+          <t>CVE-2026-101891</t>
+        </is>
+      </c>
+      <c r="B3415" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3415" t="inlineStr">
+        <is>
+          <t>WatchGuard Patches Critical Fireware OS Code Injection Vulnerability</t>
+        </is>
+      </c>
+      <c r="D3415" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/watchguard-patches-critical-fireware-os-code-injection-vulnerability/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3416">
+      <c r="A3416" t="inlineStr">
+        <is>
+          <t>CVE-2026-86131</t>
+        </is>
+      </c>
+      <c r="B3416" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3416" t="inlineStr">
+        <is>
+          <t>WatchGuard Patches Critical Fireware OS Code Injection Vulnerability</t>
+        </is>
+      </c>
+      <c r="D3416" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/watchguard-patches-critical-fireware-os-code-injection-vulnerability/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3416"/>
+  <dimension ref="A1:D3418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75568,6 +75568,50 @@
         </is>
       </c>
     </row>
+    <row r="3417">
+      <c r="A3417" t="inlineStr">
+        <is>
+          <t>CVE-2026-1731</t>
+        </is>
+      </c>
+      <c r="B3417" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3417" t="inlineStr">
+        <is>
+          <t>Google: AI Is Changing the Pace and Profile of Vulnerability Discovery</t>
+        </is>
+      </c>
+      <c r="D3417" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/google-ai-is-changing-the-pace-and-profile-of-vulnerability-discovery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3418">
+      <c r="A3418" t="inlineStr">
+        <is>
+          <t>CVE-2026-65660</t>
+        </is>
+      </c>
+      <c r="B3418" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C3418" t="inlineStr">
+        <is>
+          <t>Google: AI Is Changing the Pace and Profile of Vulnerability Discovery</t>
+        </is>
+      </c>
+      <c r="D3418" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/google-ai-is-changing-the-pace-and-profile-of-vulnerability-discovery/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3418"/>
+  <dimension ref="A1:D3419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75612,6 +75612,28 @@
         </is>
       </c>
     </row>
+    <row r="3419">
+      <c r="A3419" t="inlineStr">
+        <is>
+          <t>CVE-2026-76504</t>
+        </is>
+      </c>
+      <c r="B3419" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C3419" t="inlineStr">
+        <is>
+          <t>Cisco Patches Exploited Catalyst SD-WAN Zero-Day Vulnerability</t>
+        </is>
+      </c>
+      <c r="D3419" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-exploited-catalyst-sd-wan-zero-day-vulnerability/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3419"/>
+  <dimension ref="A1:D3421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75634,6 +75634,50 @@
         </is>
       </c>
     </row>
+    <row r="3420">
+      <c r="A3420" t="inlineStr">
+        <is>
+          <t>CVE-2026-102489</t>
+        </is>
+      </c>
+      <c r="B3420" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C3420" t="inlineStr">
+        <is>
+          <t>Zammad Zero-Days Exploited in AI-Powered DIVD Hack</t>
+        </is>
+      </c>
+      <c r="D3420" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/zammad-zero-days-exploited-in-ai-powered-divd-hack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3421">
+      <c r="A3421" t="inlineStr">
+        <is>
+          <t>CVE-2026-102490</t>
+        </is>
+      </c>
+      <c r="B3421" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C3421" t="inlineStr">
+        <is>
+          <t>Zammad Zero-Days Exploited in AI-Powered DIVD Hack</t>
+        </is>
+      </c>
+      <c r="D3421" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/zammad-zero-days-exploited-in-ai-powered-divd-hack/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3421"/>
+  <dimension ref="A1:D3422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75678,6 +75678,28 @@
         </is>
       </c>
     </row>
+    <row r="3422">
+      <c r="A3422" t="inlineStr">
+        <is>
+          <t>CVE-2026-73570</t>
+        </is>
+      </c>
+      <c r="B3422" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C3422" t="inlineStr">
+        <is>
+          <t>Zimbra Vulnerability Exploited in the Wild Prior to Public Disclosure</t>
+        </is>
+      </c>
+      <c r="D3422" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/zimbra-vulnerability-exploited-in-the-wild-prior-to-public-disclosure/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3422"/>
+  <dimension ref="A1:D3423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75700,6 +75700,28 @@
         </is>
       </c>
     </row>
+    <row r="3423">
+      <c r="A3423" t="inlineStr">
+        <is>
+          <t>CVE-2026-104286</t>
+        </is>
+      </c>
+      <c r="B3423" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3423" t="inlineStr">
+        <is>
+          <t>Exploited Fortinet FortiMail Zero-Day Calls for Urgent Action</t>
+        </is>
+      </c>
+      <c r="D3423" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/exploited-fortinet-fortimail-zero-day-calls-for-urgent-action/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3423"/>
+  <dimension ref="A1:D3429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75722,6 +75722,138 @@
         </is>
       </c>
     </row>
+    <row r="3424">
+      <c r="A3424" t="inlineStr">
+        <is>
+          <t>CVE-2026-45659</t>
+        </is>
+      </c>
+      <c r="B3424" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3424" t="inlineStr">
+        <is>
+          <t>Warlock Expands SharePoint Exploitation in Critical Infrastructure Attacks</t>
+        </is>
+      </c>
+      <c r="D3424" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/warlock-expands-sharepoint-exploitation-in-critical-infrastructure-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3425">
+      <c r="A3425" t="inlineStr">
+        <is>
+          <t>CVE-2026-56164</t>
+        </is>
+      </c>
+      <c r="B3425" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3425" t="inlineStr">
+        <is>
+          <t>Warlock Expands SharePoint Exploitation in Critical Infrastructure Attacks</t>
+        </is>
+      </c>
+      <c r="D3425" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/warlock-expands-sharepoint-exploitation-in-critical-infrastructure-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3426">
+      <c r="A3426" t="inlineStr">
+        <is>
+          <t>CVE-2026-50522</t>
+        </is>
+      </c>
+      <c r="B3426" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3426" t="inlineStr">
+        <is>
+          <t>Warlock Expands SharePoint Exploitation in Critical Infrastructure Attacks</t>
+        </is>
+      </c>
+      <c r="D3426" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/warlock-expands-sharepoint-exploitation-in-critical-infrastructure-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3427">
+      <c r="A3427" t="inlineStr">
+        <is>
+          <t>CVE-2026-55040</t>
+        </is>
+      </c>
+      <c r="B3427" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3427" t="inlineStr">
+        <is>
+          <t>Warlock Expands SharePoint Exploitation in Critical Infrastructure Attacks</t>
+        </is>
+      </c>
+      <c r="D3427" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/warlock-expands-sharepoint-exploitation-in-critical-infrastructure-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3428">
+      <c r="A3428" t="inlineStr">
+        <is>
+          <t>CVE-2026-58644</t>
+        </is>
+      </c>
+      <c r="B3428" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3428" t="inlineStr">
+        <is>
+          <t>Warlock Expands SharePoint Exploitation in Critical Infrastructure Attacks</t>
+        </is>
+      </c>
+      <c r="D3428" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/warlock-expands-sharepoint-exploitation-in-critical-infrastructure-attacks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3429">
+      <c r="A3429" t="inlineStr">
+        <is>
+          <t>CVE-2026-32201</t>
+        </is>
+      </c>
+      <c r="B3429" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C3429" t="inlineStr">
+        <is>
+          <t>Warlock Expands SharePoint Exploitation in Critical Infrastructure Attacks</t>
+        </is>
+      </c>
+      <c r="D3429" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/warlock-expands-sharepoint-exploitation-in-critical-infrastructure-attacks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3429"/>
+  <dimension ref="A1:D3432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75854,6 +75854,72 @@
         </is>
       </c>
     </row>
+    <row r="3430">
+      <c r="A3430" t="inlineStr">
+        <is>
+          <t>CVE-2026-79898</t>
+        </is>
+      </c>
+      <c r="B3430" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C3430" t="inlineStr">
+        <is>
+          <t>Fortra Patches Critical Vulnerabilities in BoKS</t>
+        </is>
+      </c>
+      <c r="D3430" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/fortra-patches-critical-vulnerabilities-in-boks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3431">
+      <c r="A3431" t="inlineStr">
+        <is>
+          <t>CVE-2026-12627</t>
+        </is>
+      </c>
+      <c r="B3431" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C3431" t="inlineStr">
+        <is>
+          <t>Fortra Patches Critical Vulnerabilities in BoKS</t>
+        </is>
+      </c>
+      <c r="D3431" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/fortra-patches-critical-vulnerabilities-in-boks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3432">
+      <c r="A3432" t="inlineStr">
+        <is>
+          <t>CVE-2026-79901</t>
+        </is>
+      </c>
+      <c r="B3432" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C3432" t="inlineStr">
+        <is>
+          <t>Fortra Patches Critical Vulnerabilities in BoKS</t>
+        </is>
+      </c>
+      <c r="D3432" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/fortra-patches-critical-vulnerabilities-in-boks/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3432"/>
+  <dimension ref="A1:D3435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75920,6 +75920,72 @@
         </is>
       </c>
     </row>
+    <row r="3433">
+      <c r="A3433" t="inlineStr">
+        <is>
+          <t>CVE-2026-88771</t>
+        </is>
+      </c>
+      <c r="B3433" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3433" t="inlineStr">
+        <is>
+          <t>Exploitation of Citrix NetScaler Zero-Day Hits Appliances Patched Days Earlier</t>
+        </is>
+      </c>
+      <c r="D3433" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/exploitation-of-citrix-netscaler-zero-day-hits-appliances-patched-days-earlier/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3434">
+      <c r="A3434" t="inlineStr">
+        <is>
+          <t>CVE-2026-88779</t>
+        </is>
+      </c>
+      <c r="B3434" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3434" t="inlineStr">
+        <is>
+          <t>Exploitation of Citrix NetScaler Zero-Day Hits Appliances Patched Days Earlier</t>
+        </is>
+      </c>
+      <c r="D3434" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/exploitation-of-citrix-netscaler-zero-day-hits-appliances-patched-days-earlier/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3435">
+      <c r="A3435" t="inlineStr">
+        <is>
+          <t>CVE-2026-88772</t>
+        </is>
+      </c>
+      <c r="B3435" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3435" t="inlineStr">
+        <is>
+          <t>Exploitation of Citrix NetScaler Zero-Day Hits Appliances Patched Days Earlier</t>
+        </is>
+      </c>
+      <c r="D3435" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/exploitation-of-citrix-netscaler-zero-day-hits-appliances-patched-days-earlier/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3435"/>
+  <dimension ref="A1:D3436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75986,6 +75986,28 @@
         </is>
       </c>
     </row>
+    <row r="3436">
+      <c r="A3436" t="inlineStr">
+        <is>
+          <t>CVE-2026-61500</t>
+        </is>
+      </c>
+      <c r="B3436" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C3436" t="inlineStr">
+        <is>
+          <t>Exploitation Hits Rejetto HFS Vulnerability Discovered by AI</t>
+        </is>
+      </c>
+      <c r="D3436" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/exploitation-hits-rejetto-hfs-vulnerability-discovered-by-ai/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3436"/>
+  <dimension ref="A1:D3437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76008,6 +76008,28 @@
         </is>
       </c>
     </row>
+    <row r="3437">
+      <c r="A3437" t="inlineStr">
+        <is>
+          <t>CVE-2026-21589</t>
+        </is>
+      </c>
+      <c r="B3437" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C3437" t="inlineStr">
+        <is>
+          <t>Atlassian Patches Critical Vulnerability Affecting 8 Products</t>
+        </is>
+      </c>
+      <c r="D3437" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/atlassian-patches-critical-vulnerability-affecting-8-products/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3437"/>
+  <dimension ref="A1:D3441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76030,6 +76030,94 @@
         </is>
       </c>
     </row>
+    <row r="3438">
+      <c r="A3438" t="inlineStr">
+        <is>
+          <t>CVE-2026-106382</t>
+        </is>
+      </c>
+      <c r="B3438" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C3438" t="inlineStr">
+        <is>
+          <t>Chrome 155 Update Patches 247 Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3438" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chrome-155-update-patches-247-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3439">
+      <c r="A3439" t="inlineStr">
+        <is>
+          <t>CVE-2026-106358</t>
+        </is>
+      </c>
+      <c r="B3439" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C3439" t="inlineStr">
+        <is>
+          <t>Chrome 155 Update Patches 247 Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3439" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chrome-155-update-patches-247-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3440">
+      <c r="A3440" t="inlineStr">
+        <is>
+          <t>CVE-2026-106347</t>
+        </is>
+      </c>
+      <c r="B3440" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C3440" t="inlineStr">
+        <is>
+          <t>Chrome 155 Update Patches 247 Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3440" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chrome-155-update-patches-247-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3441">
+      <c r="A3441" t="inlineStr">
+        <is>
+          <t>CVE-2026-106197</t>
+        </is>
+      </c>
+      <c r="B3441" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C3441" t="inlineStr">
+        <is>
+          <t>Chrome 155 Update Patches 247 Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3441" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chrome-155-update-patches-247-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3441"/>
+  <dimension ref="A1:D3446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76118,6 +76118,116 @@
         </is>
       </c>
     </row>
+    <row r="3442">
+      <c r="A3442" t="inlineStr">
+        <is>
+          <t>CVE-2025-30239</t>
+        </is>
+      </c>
+      <c r="B3442" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3442" t="inlineStr">
+        <is>
+          <t>TP-Link Faces State Lawsuits and New Scrutiny Over ISP Router Flaws</t>
+        </is>
+      </c>
+      <c r="D3442" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/tp-link-faces-state-lawsuits-and-new-scrutiny-over-isp-router-flaws/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3443">
+      <c r="A3443" t="inlineStr">
+        <is>
+          <t>CVE-2025-30237</t>
+        </is>
+      </c>
+      <c r="B3443" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3443" t="inlineStr">
+        <is>
+          <t>TP-Link Faces State Lawsuits and New Scrutiny Over ISP Router Flaws</t>
+        </is>
+      </c>
+      <c r="D3443" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/tp-link-faces-state-lawsuits-and-new-scrutiny-over-isp-router-flaws/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3444">
+      <c r="A3444" t="inlineStr">
+        <is>
+          <t>CVE-2025-30240</t>
+        </is>
+      </c>
+      <c r="B3444" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3444" t="inlineStr">
+        <is>
+          <t>TP-Link Faces State Lawsuits and New Scrutiny Over ISP Router Flaws</t>
+        </is>
+      </c>
+      <c r="D3444" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/tp-link-faces-state-lawsuits-and-new-scrutiny-over-isp-router-flaws/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3445">
+      <c r="A3445" t="inlineStr">
+        <is>
+          <t>CVE-2025-30238</t>
+        </is>
+      </c>
+      <c r="B3445" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3445" t="inlineStr">
+        <is>
+          <t>TP-Link Faces State Lawsuits and New Scrutiny Over ISP Router Flaws</t>
+        </is>
+      </c>
+      <c r="D3445" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/tp-link-faces-state-lawsuits-and-new-scrutiny-over-isp-router-flaws/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3446">
+      <c r="A3446" t="inlineStr">
+        <is>
+          <t>CVE-2025-30241</t>
+        </is>
+      </c>
+      <c r="B3446" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3446" t="inlineStr">
+        <is>
+          <t>TP-Link Faces State Lawsuits and New Scrutiny Over ISP Router Flaws</t>
+        </is>
+      </c>
+      <c r="D3446" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/tp-link-faces-state-lawsuits-and-new-scrutiny-over-isp-router-flaws/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3446"/>
+  <dimension ref="A1:D3447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76228,6 +76228,28 @@
         </is>
       </c>
     </row>
+    <row r="3447">
+      <c r="A3447" t="inlineStr">
+        <is>
+          <t>CVE-2026-102255</t>
+        </is>
+      </c>
+      <c r="B3447" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3447" t="inlineStr">
+        <is>
+          <t>SonicWall and Splunk Patch Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3447" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/sonicwall-and-splunk-patch-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3447"/>
+  <dimension ref="A1:D3448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76250,6 +76250,28 @@
         </is>
       </c>
     </row>
+    <row r="3448">
+      <c r="A3448" t="inlineStr">
+        <is>
+          <t>CVE-2026-21589</t>
+        </is>
+      </c>
+      <c r="B3448" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3448" t="inlineStr">
+        <is>
+          <t>Attackers Target Critical Atlassian Vulnerability Within Hours of PoC Publication</t>
+        </is>
+      </c>
+      <c r="D3448" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/attackers-target-critical-atlassian-vulnerability-within-hours-of-poc-publication/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3448"/>
+  <dimension ref="A1:D3465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76272,6 +76272,380 @@
         </is>
       </c>
     </row>
+    <row r="3449">
+      <c r="A3449" t="inlineStr">
+        <is>
+          <t>CVE-2026-76483</t>
+        </is>
+      </c>
+      <c r="B3449" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3449" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3449" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3450">
+      <c r="A3450" t="inlineStr">
+        <is>
+          <t>CVE-2026-76471</t>
+        </is>
+      </c>
+      <c r="B3450" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3450" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3450" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3451">
+      <c r="A3451" t="inlineStr">
+        <is>
+          <t>CVE-2026-76482</t>
+        </is>
+      </c>
+      <c r="B3451" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3451" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3451" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3452">
+      <c r="A3452" t="inlineStr">
+        <is>
+          <t>CVE-2026-76500</t>
+        </is>
+      </c>
+      <c r="B3452" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3452" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3452" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3453">
+      <c r="A3453" t="inlineStr">
+        <is>
+          <t>CVE-2026-76501</t>
+        </is>
+      </c>
+      <c r="B3453" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3453" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3453" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3454">
+      <c r="A3454" t="inlineStr">
+        <is>
+          <t>CVE-2026-76499</t>
+        </is>
+      </c>
+      <c r="B3454" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3454" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3454" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3455">
+      <c r="A3455" t="inlineStr">
+        <is>
+          <t>CVE-2026-20362</t>
+        </is>
+      </c>
+      <c r="B3455" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3455" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3455" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3456">
+      <c r="A3456" t="inlineStr">
+        <is>
+          <t>CVE-2026-76480</t>
+        </is>
+      </c>
+      <c r="B3456" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3456" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3456" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3457">
+      <c r="A3457" t="inlineStr">
+        <is>
+          <t>CVE-2026-76464</t>
+        </is>
+      </c>
+      <c r="B3457" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3457" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3457" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3458">
+      <c r="A3458" t="inlineStr">
+        <is>
+          <t>CVE-2026-76455</t>
+        </is>
+      </c>
+      <c r="B3458" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3458" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3458" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3459">
+      <c r="A3459" t="inlineStr">
+        <is>
+          <t>CVE-2026-76454</t>
+        </is>
+      </c>
+      <c r="B3459" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3459" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3459" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3460">
+      <c r="A3460" t="inlineStr">
+        <is>
+          <t>CVE-2026-20328</t>
+        </is>
+      </c>
+      <c r="B3460" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3460" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3460" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3461">
+      <c r="A3461" t="inlineStr">
+        <is>
+          <t>CVE-2026-76486</t>
+        </is>
+      </c>
+      <c r="B3461" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3461" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3461" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3462">
+      <c r="A3462" t="inlineStr">
+        <is>
+          <t>CVE-2026-76498</t>
+        </is>
+      </c>
+      <c r="B3462" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3462" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3462" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3463">
+      <c r="A3463" t="inlineStr">
+        <is>
+          <t>CVE-2026-76465</t>
+        </is>
+      </c>
+      <c r="B3463" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3463" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3463" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3464">
+      <c r="A3464" t="inlineStr">
+        <is>
+          <t>CVE-2026-76459</t>
+        </is>
+      </c>
+      <c r="B3464" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3464" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3464" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3465">
+      <c r="A3465" t="inlineStr">
+        <is>
+          <t>CVE-2026-76485</t>
+        </is>
+      </c>
+      <c r="B3465" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C3465" t="inlineStr">
+        <is>
+          <t>Cisco Patches a Dozen Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3465" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-patches-a-dozen-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3465"/>
+  <dimension ref="A1:D3469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76646,6 +76646,94 @@
         </is>
       </c>
     </row>
+    <row r="3466">
+      <c r="A3466" t="inlineStr">
+        <is>
+          <t>CVE-2026-88771</t>
+        </is>
+      </c>
+      <c r="B3466" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3466" t="inlineStr">
+        <is>
+          <t>Citrix Urges Immediate Patching of Critical NetScaler Vulnerability</t>
+        </is>
+      </c>
+      <c r="D3466" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-urges-immediate-patching-of-critical-netscaler-vulnerability/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3467">
+      <c r="A3467" t="inlineStr">
+        <is>
+          <t>CVE-2026-88772</t>
+        </is>
+      </c>
+      <c r="B3467" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3467" t="inlineStr">
+        <is>
+          <t>Citrix Urges Immediate Patching of Critical NetScaler Vulnerability</t>
+        </is>
+      </c>
+      <c r="D3467" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-urges-immediate-patching-of-critical-netscaler-vulnerability/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3468">
+      <c r="A3468" t="inlineStr">
+        <is>
+          <t>CVE-2026-107406</t>
+        </is>
+      </c>
+      <c r="B3468" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3468" t="inlineStr">
+        <is>
+          <t>Citrix Urges Immediate Patching of Critical NetScaler Vulnerability</t>
+        </is>
+      </c>
+      <c r="D3468" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-urges-immediate-patching-of-critical-netscaler-vulnerability/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3469">
+      <c r="A3469" t="inlineStr">
+        <is>
+          <t>CVE-2026-88779</t>
+        </is>
+      </c>
+      <c r="B3469" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3469" t="inlineStr">
+        <is>
+          <t>Citrix Urges Immediate Patching of Critical NetScaler Vulnerability</t>
+        </is>
+      </c>
+      <c r="D3469" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-urges-immediate-patching-of-critical-netscaler-vulnerability/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3469"/>
+  <dimension ref="A1:D3471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76734,6 +76734,50 @@
         </is>
       </c>
     </row>
+    <row r="3470">
+      <c r="A3470" t="inlineStr">
+        <is>
+          <t>CVE-2026-105134</t>
+        </is>
+      </c>
+      <c r="B3470" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3470" t="inlineStr">
+        <is>
+          <t>Unpatched AhsayCBS Vulnerabilities Exploited in the Wild</t>
+        </is>
+      </c>
+      <c r="D3470" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/unpatched-ahsaycbs-vulnerabilities-exploited-in-the-wild/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3471">
+      <c r="A3471" t="inlineStr">
+        <is>
+          <t>CVE-2026-105133</t>
+        </is>
+      </c>
+      <c r="B3471" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C3471" t="inlineStr">
+        <is>
+          <t>Unpatched AhsayCBS Vulnerabilities Exploited in the Wild</t>
+        </is>
+      </c>
+      <c r="D3471" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/unpatched-ahsaycbs-vulnerabilities-exploited-in-the-wild/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3471"/>
+  <dimension ref="A1:D3472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76778,6 +76778,28 @@
         </is>
       </c>
     </row>
+    <row r="3472">
+      <c r="A3472" t="inlineStr">
+        <is>
+          <t>CVE-2026-102255</t>
+        </is>
+      </c>
+      <c r="B3472" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C3472" t="inlineStr">
+        <is>
+          <t>Critical SonicWall Vulnerability Exploited Days After Disclosure</t>
+        </is>
+      </c>
+      <c r="D3472" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/critical-sonicwall-vulnerability-exploited-days-after-disclosure/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3472"/>
+  <dimension ref="A1:D3473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76800,6 +76800,28 @@
         </is>
       </c>
     </row>
+    <row r="3473">
+      <c r="A3473" t="inlineStr">
+        <is>
+          <t>CVE-2026-85097</t>
+        </is>
+      </c>
+      <c r="B3473" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C3473" t="inlineStr">
+        <is>
+          <t>Bricksforge WordPress Plugin Vulnerability Exploited in the Wild</t>
+        </is>
+      </c>
+      <c r="D3473" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/bricksforge-wordpress-plugin-vulnerability-exploited-in-the-wild/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3473"/>
+  <dimension ref="A1:D3474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76822,6 +76822,28 @@
         </is>
       </c>
     </row>
+    <row r="3474">
+      <c r="A3474" t="inlineStr">
+        <is>
+          <t>CVE-2026-104935</t>
+        </is>
+      </c>
+      <c r="B3474" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C3474" t="inlineStr">
+        <is>
+          <t>Ivanti Zero-Day Chain Gave Attackers Root Access to Fully Patched VPN</t>
+        </is>
+      </c>
+      <c r="D3474" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/ivanti-zero-day-chain-gave-attackers-root-access-to-fully-patched-vpn/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3474"/>
+  <dimension ref="A1:D3478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76844,6 +76844,94 @@
         </is>
       </c>
     </row>
+    <row r="3475">
+      <c r="A3475" t="inlineStr">
+        <is>
+          <t>CVE-2026-89108</t>
+        </is>
+      </c>
+      <c r="B3475" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C3475" t="inlineStr">
+        <is>
+          <t>SAP Patches Critical NetWeaver, S/4HANA Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3475" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/sap-patches-critical-netweaver-s-4hana-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3476">
+      <c r="A3476" t="inlineStr">
+        <is>
+          <t>CVE-2026-89110</t>
+        </is>
+      </c>
+      <c r="B3476" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C3476" t="inlineStr">
+        <is>
+          <t>SAP Patches Critical NetWeaver, S/4HANA Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3476" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/sap-patches-critical-netweaver-s-4hana-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3477">
+      <c r="A3477" t="inlineStr">
+        <is>
+          <t>CVE-2026-89107</t>
+        </is>
+      </c>
+      <c r="B3477" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C3477" t="inlineStr">
+        <is>
+          <t>SAP Patches Critical NetWeaver, S/4HANA Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3477" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/sap-patches-critical-netweaver-s-4hana-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3478">
+      <c r="A3478" t="inlineStr">
+        <is>
+          <t>CVE-2026-89111</t>
+        </is>
+      </c>
+      <c r="B3478" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C3478" t="inlineStr">
+        <is>
+          <t>SAP Patches Critical NetWeaver, S/4HANA Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3478" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/sap-patches-critical-netweaver-s-4hana-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3478"/>
+  <dimension ref="A1:D3486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76932,6 +76932,182 @@
         </is>
       </c>
     </row>
+    <row r="3479">
+      <c r="A3479" t="inlineStr">
+        <is>
+          <t>CVE-2026-109412</t>
+        </is>
+      </c>
+      <c r="B3479" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C3479" t="inlineStr">
+        <is>
+          <t>Citrix, Fortinet, Ivanti Patch 29 Vulnerabilities Across Their Products</t>
+        </is>
+      </c>
+      <c r="D3479" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-fortinet-ivanti-patch-29-vulnerabilities-across-their-products/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3480">
+      <c r="A3480" t="inlineStr">
+        <is>
+          <t>CVE-2026-107656</t>
+        </is>
+      </c>
+      <c r="B3480" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C3480" t="inlineStr">
+        <is>
+          <t>Citrix, Fortinet, Ivanti Patch 29 Vulnerabilities Across Their Products</t>
+        </is>
+      </c>
+      <c r="D3480" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-fortinet-ivanti-patch-29-vulnerabilities-across-their-products/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3481">
+      <c r="A3481" t="inlineStr">
+        <is>
+          <t>CVE-2026-104935</t>
+        </is>
+      </c>
+      <c r="B3481" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C3481" t="inlineStr">
+        <is>
+          <t>Citrix, Fortinet, Ivanti Patch 29 Vulnerabilities Across Their Products</t>
+        </is>
+      </c>
+      <c r="D3481" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-fortinet-ivanti-patch-29-vulnerabilities-across-their-products/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3482">
+      <c r="A3482" t="inlineStr">
+        <is>
+          <t>CVE-2026-106173</t>
+        </is>
+      </c>
+      <c r="B3482" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C3482" t="inlineStr">
+        <is>
+          <t>Citrix, Fortinet, Ivanti Patch 29 Vulnerabilities Across Their Products</t>
+        </is>
+      </c>
+      <c r="D3482" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-fortinet-ivanti-patch-29-vulnerabilities-across-their-products/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3483">
+      <c r="A3483" t="inlineStr">
+        <is>
+          <t>CVE-2026-106042</t>
+        </is>
+      </c>
+      <c r="B3483" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C3483" t="inlineStr">
+        <is>
+          <t>Citrix, Fortinet, Ivanti Patch 29 Vulnerabilities Across Their Products</t>
+        </is>
+      </c>
+      <c r="D3483" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/citrix-fortinet-ivanti-patch-29-vulnerabilities-across-their-products/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3484">
+      <c r="A3484" t="inlineStr">
+        <is>
+          <t>CVE-2026-108398</t>
+        </is>
+      </c>
+      <c r="B3484" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C3484" t="inlineStr">
+        <is>
+          <t>Microsoft Patches Record 1,413 Vulnerabilities, Including Exploited Windows Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3484" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/microsoft-patches-record-1413-vulnerabilities-including-exploited-windows-zero-day/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3485">
+      <c r="A3485" t="inlineStr">
+        <is>
+          <t>CVE-2026-92707</t>
+        </is>
+      </c>
+      <c r="B3485" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C3485" t="inlineStr">
+        <is>
+          <t>Microsoft Patches Record 1,413 Vulnerabilities, Including Exploited Windows Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3485" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/microsoft-patches-record-1413-vulnerabilities-including-exploited-windows-zero-day/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3486">
+      <c r="A3486" t="inlineStr">
+        <is>
+          <t>CVE-2026-96951</t>
+        </is>
+      </c>
+      <c r="B3486" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C3486" t="inlineStr">
+        <is>
+          <t>Microsoft Patches Record 1,413 Vulnerabilities, Including Exploited Windows Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3486" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/microsoft-patches-record-1413-vulnerabilities-including-exploited-windows-zero-day/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3486"/>
+  <dimension ref="A1:D3490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77108,6 +77108,94 @@
         </is>
       </c>
     </row>
+    <row r="3487">
+      <c r="A3487" t="inlineStr">
+        <is>
+          <t>CVE-2026-0322</t>
+        </is>
+      </c>
+      <c r="B3487" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C3487" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks Patches PAN-OS Zero-Day Exploited for Remote Code Execution</t>
+        </is>
+      </c>
+      <c r="D3487" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/palo-alto-networks-patches-pan-os-zero-day-exploited-for-remote-code-execution/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3488">
+      <c r="A3488" t="inlineStr">
+        <is>
+          <t>CVE-2026-76461</t>
+        </is>
+      </c>
+      <c r="B3488" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C3488" t="inlineStr">
+        <is>
+          <t>Cisco Warns of Exploited Secure Email Gateway Vulnerability</t>
+        </is>
+      </c>
+      <c r="D3488" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-warns-of-exploited-secure-email-gateway-vulnerability/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3489">
+      <c r="A3489" t="inlineStr">
+        <is>
+          <t>CVE-2026-76519</t>
+        </is>
+      </c>
+      <c r="B3489" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C3489" t="inlineStr">
+        <is>
+          <t>Cisco Warns of Exploited Secure Email Gateway Vulnerability</t>
+        </is>
+      </c>
+      <c r="D3489" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-warns-of-exploited-secure-email-gateway-vulnerability/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3490">
+      <c r="A3490" t="inlineStr">
+        <is>
+          <t>CVE-2026-76440</t>
+        </is>
+      </c>
+      <c r="B3490" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C3490" t="inlineStr">
+        <is>
+          <t>Cisco Warns of Exploited Secure Email Gateway Vulnerability</t>
+        </is>
+      </c>
+      <c r="D3490" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/cisco-warns-of-exploited-secure-email-gateway-vulnerability/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3490"/>
+  <dimension ref="A1:D3493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77196,6 +77196,72 @@
         </is>
       </c>
     </row>
+    <row r="3491">
+      <c r="A3491" t="inlineStr">
+        <is>
+          <t>CVE-2026-15176</t>
+        </is>
+      </c>
+      <c r="B3491" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C3491" t="inlineStr">
+        <is>
+          <t>F5, Juniper Networks Patch Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3491" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/f5-juniper-networks-patch-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3492">
+      <c r="A3492" t="inlineStr">
+        <is>
+          <t>CVE-2026-93479</t>
+        </is>
+      </c>
+      <c r="B3492" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C3492" t="inlineStr">
+        <is>
+          <t>F5, Juniper Networks Patch Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3492" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/f5-juniper-networks-patch-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3493">
+      <c r="A3493" t="inlineStr">
+        <is>
+          <t>CVE-2026-97205</t>
+        </is>
+      </c>
+      <c r="B3493" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C3493" t="inlineStr">
+        <is>
+          <t>F5, Juniper Networks Patch Critical Vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D3493" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/f5-juniper-networks-patch-critical-vulnerabilities/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3493"/>
+  <dimension ref="A1:D3499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77262,6 +77262,138 @@
         </is>
       </c>
     </row>
+    <row r="3494">
+      <c r="A3494" t="inlineStr">
+        <is>
+          <t>CVE-2023-4966</t>
+        </is>
+      </c>
+      <c r="B3494" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C3494" t="inlineStr">
+        <is>
+          <t>Chinese APT Exploited BeyondTrust Vulnerability as Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3494" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chinese-apt-exploited-beyondtrust-vulnerability-as-zero-day/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3495">
+      <c r="A3495" t="inlineStr">
+        <is>
+          <t>CVE-2023-46805</t>
+        </is>
+      </c>
+      <c r="B3495" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C3495" t="inlineStr">
+        <is>
+          <t>Chinese APT Exploited BeyondTrust Vulnerability as Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3495" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chinese-apt-exploited-beyondtrust-vulnerability-as-zero-day/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3496">
+      <c r="A3496" t="inlineStr">
+        <is>
+          <t>CVE-2026-102764</t>
+        </is>
+      </c>
+      <c r="B3496" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C3496" t="inlineStr">
+        <is>
+          <t>Chinese APT Exploited BeyondTrust Vulnerability as Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3496" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chinese-apt-exploited-beyondtrust-vulnerability-as-zero-day/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3497">
+      <c r="A3497" t="inlineStr">
+        <is>
+          <t>CVE-2026-22769</t>
+        </is>
+      </c>
+      <c r="B3497" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C3497" t="inlineStr">
+        <is>
+          <t>Chinese APT Exploited BeyondTrust Vulnerability as Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3497" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chinese-apt-exploited-beyondtrust-vulnerability-as-zero-day/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3498">
+      <c r="A3498" t="inlineStr">
+        <is>
+          <t>CVE-2024-21887</t>
+        </is>
+      </c>
+      <c r="B3498" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C3498" t="inlineStr">
+        <is>
+          <t>Chinese APT Exploited BeyondTrust Vulnerability as Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3498" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chinese-apt-exploited-beyondtrust-vulnerability-as-zero-day/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3499">
+      <c r="A3499" t="inlineStr">
+        <is>
+          <t>CVE-2025-0282</t>
+        </is>
+      </c>
+      <c r="B3499" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C3499" t="inlineStr">
+        <is>
+          <t>Chinese APT Exploited BeyondTrust Vulnerability as Zero-Day</t>
+        </is>
+      </c>
+      <c r="D3499" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/chinese-apt-exploited-beyondtrust-vulnerability-as-zero-day/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3499"/>
+  <dimension ref="A1:D3502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77394,6 +77394,72 @@
         </is>
       </c>
     </row>
+    <row r="3500">
+      <c r="A3500" t="inlineStr">
+        <is>
+          <t>CVE-2024-26008</t>
+        </is>
+      </c>
+      <c r="B3500" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C3500" t="inlineStr">
+        <is>
+          <t>Exploited Fortinet Bug Linked to Stealthy FortiGate Implant in Telecom Hack</t>
+        </is>
+      </c>
+      <c r="D3500" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/exploited-fortinet-bug-linked-to-stealthy-fortigate-implant-in-telecom-hack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3501">
+      <c r="A3501" t="inlineStr">
+        <is>
+          <t>CVE-2024-47575</t>
+        </is>
+      </c>
+      <c r="B3501" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C3501" t="inlineStr">
+        <is>
+          <t>Exploited Fortinet Bug Linked to Stealthy FortiGate Implant in Telecom Hack</t>
+        </is>
+      </c>
+      <c r="D3501" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/exploited-fortinet-bug-linked-to-stealthy-fortigate-implant-in-telecom-hack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3502">
+      <c r="A3502" t="inlineStr">
+        <is>
+          <t>CVE-2025-61624</t>
+        </is>
+      </c>
+      <c r="B3502" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C3502" t="inlineStr">
+        <is>
+          <t>Exploited Fortinet Bug Linked to Stealthy FortiGate Implant in Telecom Hack</t>
+        </is>
+      </c>
+      <c r="D3502" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/exploited-fortinet-bug-linked-to-stealthy-fortigate-implant-in-telecom-hack/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3502"/>
+  <dimension ref="A1:D3506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77460,6 +77460,94 @@
         </is>
       </c>
     </row>
+    <row r="3503">
+      <c r="A3503" t="inlineStr">
+        <is>
+          <t>CVE-2026-96654</t>
+        </is>
+      </c>
+      <c r="B3503" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C3503" t="inlineStr">
+        <is>
+          <t>Plex2Shell Exploit Chain Weaponized Against Plex Servers Hours After Disclosure</t>
+        </is>
+      </c>
+      <c r="D3503" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/plex2shell-exploit-chain-weaponized-against-plex-servers-hours-after-disclosure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3504">
+      <c r="A3504" t="inlineStr">
+        <is>
+          <t>CVE-2026-96652</t>
+        </is>
+      </c>
+      <c r="B3504" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C3504" t="inlineStr">
+        <is>
+          <t>Plex2Shell Exploit Chain Weaponized Against Plex Servers Hours After Disclosure</t>
+        </is>
+      </c>
+      <c r="D3504" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/plex2shell-exploit-chain-weaponized-against-plex-servers-hours-after-disclosure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3505">
+      <c r="A3505" t="inlineStr">
+        <is>
+          <t>CVE-2026-96656</t>
+        </is>
+      </c>
+      <c r="B3505" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C3505" t="inlineStr">
+        <is>
+          <t>Plex2Shell Exploit Chain Weaponized Against Plex Servers Hours After Disclosure</t>
+        </is>
+      </c>
+      <c r="D3505" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/plex2shell-exploit-chain-weaponized-against-plex-servers-hours-after-disclosure/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3506">
+      <c r="A3506" t="inlineStr">
+        <is>
+          <t>CVE-2026-96655</t>
+        </is>
+      </c>
+      <c r="B3506" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C3506" t="inlineStr">
+        <is>
+          <t>Plex2Shell Exploit Chain Weaponized Against Plex Servers Hours After Disclosure</t>
+        </is>
+      </c>
+      <c r="D3506" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/plex2shell-exploit-chain-weaponized-against-plex-servers-hours-after-disclosure/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/securityweek_cves.xlsx
+++ b/securityweek_cves.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3506"/>
+  <dimension ref="A1:D3510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77548,6 +77548,94 @@
         </is>
       </c>
     </row>
+    <row r="3507">
+      <c r="A3507" t="inlineStr">
+        <is>
+          <t>CVE-2026-108515</t>
+        </is>
+      </c>
+      <c r="B3507" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C3507" t="inlineStr">
+        <is>
+          <t>Drupal Warns of Fast Exploitation Risk for Critical Core RCE Flaw</t>
+        </is>
+      </c>
+      <c r="D3507" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/drupal-warns-of-fast-exploitation-risk-for-critical-core-rce-flaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3508">
+      <c r="A3508" t="inlineStr">
+        <is>
+          <t>CVE-2026-108097</t>
+        </is>
+      </c>
+      <c r="B3508" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C3508" t="inlineStr">
+        <is>
+          <t>Drupal Warns of Fast Exploitation Risk for Critical Core RCE Flaw</t>
+        </is>
+      </c>
+      <c r="D3508" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/drupal-warns-of-fast-exploitation-risk-for-critical-core-rce-flaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3509">
+      <c r="A3509" t="inlineStr">
+        <is>
+          <t>CVE-2026-108514</t>
+        </is>
+      </c>
+      <c r="B3509" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C3509" t="inlineStr">
+        <is>
+          <t>Drupal Warns of Fast Exploitation Risk for Critical Core RCE Flaw</t>
+        </is>
+      </c>
+      <c r="D3509" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/drupal-warns-of-fast-exploitation-risk-for-critical-core-rce-flaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3510">
+      <c r="A3510" t="inlineStr">
+        <is>
+          <t>CVE-2026-108099</t>
+        </is>
+      </c>
+      <c r="B3510" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C3510" t="inlineStr">
+        <is>
+          <t>Drupal Warns of Fast Exploitation Risk for Critical Core RCE Flaw</t>
+        </is>
+      </c>
+      <c r="D3510" t="inlineStr">
+        <is>
+          <t>https://www.securityweek.com/drupal-warns-of-fast-exploitation-risk-for-critical-core-rce-flaw/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
